--- a/loss-time/outputs/Loss_time_05-10_den_26-10.xlsx
+++ b/loss-time/outputs/Loss_time_05-10_den_26-10.xlsx
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">Ngày 09/10 có 8 nhân viên mới (Assembly 6, Raw Cutting Panel 2; lấy theo P22 đã nhập trên hệ thống), A2 bắt đầu từ 10/10. Ngày 10/10 chưa thấy có nhân viên mới (chờ xác nhận).</t>
   </si>
   <si>
-    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Ngày 21/10 có 5 nhân viên mới (Raw Cutting Panel 1, Machining 2, Assembly 2 gồm 1 người dưới Mr.Dũng-Inlay). Ngày 22/10 có 6 nhân viên mới (Raw Cutting Panel 3, Machining 1, Assembly 2; người ghi "0" ở cột CT/TV vẫn tính vào HC). Ngày 23/10 và 24/10 chưa có nhân viên mới (chờ báo). Thứ Bảy 24/10 mặc định không tăng ca (chờ xác nhận); Ngày 23/10 có 1 nhân viên mới Raw Cutting Panel (người ghi "0" ở cột CT/TV vẫn tính). Thứ Hai 26/10 không tăng ca (P26 và P20 Assembly 7:30-15:30), từ 26/10 A2 của các nhóm Assembly cộng thêm 1 ngày vì Chủ nhật 25/10 đã tính. Chủ nhật 25/10 chỉ Assembly làm, không tăng ca: P20 và P26 của Assembly ghi 7:30-15:30; A2 của các nhóm Assembly vẫn ghi và tính là một ngày (theo tiền lệ 27/9). Từ 19/10 đến 23/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
+    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Ngày 21/10 có 5 nhân viên mới (Raw Cutting Panel 1, Machining 2, Assembly 2 gồm 1 người dưới Mr.Dũng-Inlay). Ngày 22/10 có 6 nhân viên mới (Raw Cutting Panel 3, Machining 1, Assembly 2; người ghi "0" ở cột CT/TV vẫn tính vào HC). Ngày 23/10 và 24/10 chưa có nhân viên mới (chờ báo). Thứ Bảy 24/10 mặc định không tăng ca (chờ xác nhận); Ngày 23/10 có 1 nhân viên mới Raw Cutting Panel (người ghi "0" ở cột CT/TV vẫn tính). Thứ Hai 26/10 không tăng ca (ngày thường: P26 và P20 Assembly 7:30-16:00), từ 26/10 A2 của các nhóm Assembly cộng thêm 1 ngày vì Chủ nhật 25/10 đã tính. Chủ nhật 25/10 chỉ Assembly làm, không tăng ca: P20 và P26 của Assembly ghi 7:30-15:30; A2 của các nhóm Assembly vẫn ghi và tính là một ngày (theo tiền lệ 27/9). Từ 19/10 đến 23/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
   </si>
   <si>
     <t xml:space="preserve">Thứ Bảy 10/10 không tăng ca: P26 và P20 Assembly ghi 7:30-15:30 (sớm 30 phút so với ca ngày thường 7:30-16:00); 4 dòng P20 ngắn ghi 7:00-7:30 theo mặc định, chờ xác nhận.</t>
@@ -24777,18 +24777,18 @@
         <v>0.3125</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O7" s="7" t="n">
         <f aca="false">(N7-M7)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q7" s="7" t="n">
         <f aca="false">P7*O7</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24825,18 +24825,18 @@
         <v>0.3125</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O8" s="7" t="n">
         <f aca="false">(N8-M8)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="Q8" s="7" t="n">
         <f aca="false">P8*O8</f>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24873,18 +24873,18 @@
         <v>0.3125</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O9" s="7" t="n">
         <f aca="false">(N9-M9)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q9" s="7" t="n">
         <f aca="false">P9*O9</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24921,18 +24921,18 @@
         <v>0.3125</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O10" s="7" t="n">
         <f aca="false">(N10-M10)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q10" s="7" t="n">
         <f aca="false">P10*O10</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24969,18 +24969,18 @@
         <v>0.3125</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O11" s="7" t="n">
         <f aca="false">(N11-M11)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="7" t="n">
         <f aca="false">P11*O11</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25017,18 +25017,18 @@
         <v>0.3125</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O12" s="7" t="n">
         <f aca="false">(N12-M12)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q12" s="7" t="n">
         <f aca="false">P12*O12</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25065,18 +25065,18 @@
         <v>0.3125</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O13" s="7" t="n">
         <f aca="false">(N13-M13)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q13" s="7" t="n">
         <f aca="false">P13*O13</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25113,18 +25113,18 @@
         <v>0.3125</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O14" s="7" t="n">
         <f aca="false">(N14-M14)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="7" t="n">
         <f aca="false">P14*O14</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25161,18 +25161,18 @@
         <v>0.3125</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O15" s="7" t="n">
         <f aca="false">(N15-M15)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q15" s="7" t="n">
         <f aca="false">P15*O15</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25209,18 +25209,18 @@
         <v>0.3125</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O16" s="7" t="n">
         <f aca="false">(N16-M16)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">P16*O16</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25257,18 +25257,18 @@
         <v>0.3125</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O17" s="7" t="n">
         <f aca="false">(N17-M17)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="7" t="n">
         <f aca="false">P17*O17</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25305,18 +25305,18 @@
         <v>0.3125</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O18" s="7" t="n">
         <f aca="false">(N18-M18)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q18" s="7" t="n">
         <f aca="false">P18*O18</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25353,18 +25353,18 @@
         <v>0.3125</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O19" s="7" t="n">
         <f aca="false">(N19-M19)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q19" s="7" t="n">
         <f aca="false">P19*O19</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25401,18 +25401,18 @@
         <v>0.3125</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O20" s="7" t="n">
         <f aca="false">(N20-M20)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q20" s="7" t="n">
         <f aca="false">P20*O20</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25449,18 +25449,18 @@
         <v>0.3125</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O21" s="7" t="n">
         <f aca="false">(N21-M21)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="7" t="n">
         <f aca="false">P21*O21</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25497,18 +25497,18 @@
         <v>0.3125</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O22" s="7" t="n">
         <f aca="false">(N22-M22)*24</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="7" t="n">
         <f aca="false">P22*O22</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26381,7 +26381,7 @@
       </c>
       <c r="Q41" s="19" t="n">
         <f aca="false">SUM(Q3:Q40)</f>
-        <v>339.5</v>
+        <v>349.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="F176" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A176,'Loss time 26-10'!$G$3:$G$40,F$175)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G176" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A176,'Loss time 26-10'!$G$3:$G$40,G$175)</f>
@@ -30959,7 +30959,7 @@
       </c>
       <c r="J176" s="24" t="n">
         <f aca="false">SUM(C176:I176)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30971,19 +30971,19 @@
       </c>
       <c r="C177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,C$175)</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="D177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,D$175)</f>
-        <v>72</v>
+        <v>76.5</v>
       </c>
       <c r="E177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,E$175)</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,F$175)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,G$175)</f>
@@ -30999,7 +30999,7 @@
       </c>
       <c r="J177" s="24" t="n">
         <f aca="false">SUM(C177:I177)</f>
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31089,19 +31089,19 @@
       <c r="B180" s="25"/>
       <c r="C180" s="24" t="n">
         <f aca="false">SUM(C176:C179)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="D180" s="24" t="n">
         <f aca="false">SUM(D176:D179)</f>
-        <v>81</v>
+        <v>85.5</v>
       </c>
       <c r="E180" s="24" t="n">
         <f aca="false">SUM(E176:E179)</f>
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F180" s="24" t="n">
         <f aca="false">SUM(F176:F179)</f>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G180" s="24" t="n">
         <f aca="false">SUM(G176:G179)</f>
@@ -31117,7 +31117,7 @@
       </c>
       <c r="J180" s="24" t="n">
         <f aca="false">SUM(J176:J179)</f>
-        <v>339.5</v>
+        <v>349.5</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/loss-time/outputs/Loss_time_05-10_den_26-10.xlsx
+++ b/loss-time/outputs/Loss_time_05-10_den_26-10.xlsx
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">Ngày 09/10 có 8 nhân viên mới (Assembly 6, Raw Cutting Panel 2; lấy theo P22 đã nhập trên hệ thống), A2 bắt đầu từ 10/10. Ngày 10/10 chưa thấy có nhân viên mới (chờ xác nhận).</t>
   </si>
   <si>
-    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Ngày 21/10 có 5 nhân viên mới (Raw Cutting Panel 1, Machining 2, Assembly 2 gồm 1 người dưới Mr.Dũng-Inlay). Ngày 22/10 có 6 nhân viên mới (Raw Cutting Panel 3, Machining 1, Assembly 2; người ghi "0" ở cột CT/TV vẫn tính vào HC). Ngày 23/10 và 24/10 chưa có nhân viên mới (chờ báo). Thứ Bảy 24/10 mặc định không tăng ca (chờ xác nhận); Ngày 23/10 có 1 nhân viên mới Raw Cutting Panel (người ghi "0" ở cột CT/TV vẫn tính). Thứ Hai 26/10 không tăng ca (ngày thường: P26 và P20 Assembly 7:30-16:00), từ 26/10 A2 của các nhóm Assembly cộng thêm 1 ngày vì Chủ nhật 25/10 đã tính. Chủ nhật 25/10 chỉ Assembly làm, không tăng ca: P20 và P26 của Assembly ghi 7:30-15:30; A2 của các nhóm Assembly vẫn ghi và tính là một ngày (theo tiền lệ 27/9). Từ 19/10 đến 23/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
+    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Ngày 21/10 có 5 nhân viên mới (Raw Cutting Panel 1, Machining 2, Assembly 2 gồm 1 người dưới Mr.Dũng-Inlay). Ngày 22/10 có 6 nhân viên mới (Raw Cutting Panel 3, Machining 1, Assembly 2; người ghi "0" ở cột CT/TV vẫn tính vào HC). Ngày 23/10 và 24/10 chưa có nhân viên mới (chờ báo). Thứ Bảy 24/10 mặc định không tăng ca (chờ xác nhận); Ngày 23/10 có 1 nhân viên mới Raw Cutting Panel (người ghi "0" ở cột CT/TV vẫn tính). Thứ Hai-Thứ Sáu luôn tăng ca (26/10 theo mẫu ngày thường đến 20:00; chỉ Thứ Bảy, Chủ nhật không tăng ca), từ 26/10 A2 của các nhóm Assembly cộng thêm 1 ngày vì Chủ nhật 25/10 đã tính. Chủ nhật 25/10 chỉ Assembly làm, không tăng ca: P20 và P26 của Assembly ghi 7:30-15:30; A2 của các nhóm Assembly vẫn ghi và tính là một ngày (theo tiền lệ 27/9). Từ 19/10 đến 23/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
   </si>
   <si>
     <t xml:space="preserve">Thứ Bảy 10/10 không tăng ca: P26 và P20 Assembly ghi 7:30-15:30 (sớm 30 phút so với ca ngày thường 7:30-16:00); 4 dòng P20 ngắn ghi 7:00-7:30 theo mặc định, chờ xác nhận.</t>
@@ -24777,18 +24777,18 @@
         <v>0.3125</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O7" s="7" t="n">
         <f aca="false">(N7-M7)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q7" s="7" t="n">
         <f aca="false">P7*O7</f>
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24825,18 +24825,18 @@
         <v>0.3125</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O8" s="7" t="n">
         <f aca="false">(N8-M8)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="Q8" s="7" t="n">
         <f aca="false">P8*O8</f>
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24873,18 +24873,18 @@
         <v>0.3125</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O9" s="7" t="n">
         <f aca="false">(N9-M9)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q9" s="7" t="n">
         <f aca="false">P9*O9</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24921,18 +24921,18 @@
         <v>0.3125</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O10" s="7" t="n">
         <f aca="false">(N10-M10)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q10" s="7" t="n">
         <f aca="false">P10*O10</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24969,18 +24969,18 @@
         <v>0.3125</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O11" s="7" t="n">
         <f aca="false">(N11-M11)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="7" t="n">
         <f aca="false">P11*O11</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25017,18 +25017,18 @@
         <v>0.3125</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O12" s="7" t="n">
         <f aca="false">(N12-M12)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q12" s="7" t="n">
         <f aca="false">P12*O12</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25065,18 +25065,18 @@
         <v>0.3125</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O13" s="7" t="n">
         <f aca="false">(N13-M13)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q13" s="7" t="n">
         <f aca="false">P13*O13</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25113,18 +25113,18 @@
         <v>0.3125</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O14" s="7" t="n">
         <f aca="false">(N14-M14)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="7" t="n">
         <f aca="false">P14*O14</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25161,18 +25161,18 @@
         <v>0.3125</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O15" s="7" t="n">
         <f aca="false">(N15-M15)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q15" s="7" t="n">
         <f aca="false">P15*O15</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25209,18 +25209,18 @@
         <v>0.3125</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O16" s="7" t="n">
         <f aca="false">(N16-M16)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">P16*O16</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25257,18 +25257,18 @@
         <v>0.3125</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O17" s="7" t="n">
         <f aca="false">(N17-M17)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="7" t="n">
         <f aca="false">P17*O17</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25305,18 +25305,18 @@
         <v>0.3125</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O18" s="7" t="n">
         <f aca="false">(N18-M18)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q18" s="7" t="n">
         <f aca="false">P18*O18</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25353,18 +25353,18 @@
         <v>0.3125</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O19" s="7" t="n">
         <f aca="false">(N19-M19)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q19" s="7" t="n">
         <f aca="false">P19*O19</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25401,18 +25401,18 @@
         <v>0.3125</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O20" s="7" t="n">
         <f aca="false">(N20-M20)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q20" s="7" t="n">
         <f aca="false">P20*O20</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25449,18 +25449,18 @@
         <v>0.3125</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O21" s="7" t="n">
         <f aca="false">(N21-M21)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="7" t="n">
         <f aca="false">P21*O21</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25497,18 +25497,18 @@
         <v>0.3125</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O22" s="7" t="n">
         <f aca="false">(N22-M22)*24</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="7" t="n">
         <f aca="false">P22*O22</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26381,7 +26381,7 @@
       </c>
       <c r="Q41" s="19" t="n">
         <f aca="false">SUM(Q3:Q40)</f>
-        <v>349.5</v>
+        <v>429.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="F176" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A176,'Loss time 26-10'!$G$3:$G$40,F$175)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G176" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A176,'Loss time 26-10'!$G$3:$G$40,G$175)</f>
@@ -30959,7 +30959,7 @@
       </c>
       <c r="J176" s="24" t="n">
         <f aca="false">SUM(C176:I176)</f>
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30971,19 +30971,19 @@
       </c>
       <c r="C177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,C$175)</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="D177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,D$175)</f>
-        <v>76.5</v>
+        <v>112.5</v>
       </c>
       <c r="E177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,E$175)</f>
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,F$175)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G177" s="23" t="n">
         <f aca="false">SUMIFS('Loss time 26-10'!$Q$3:$Q$40,'Loss time 26-10'!$H$3:$H$40,$A177,'Loss time 26-10'!$G$3:$G$40,G$175)</f>
@@ -30999,7 +30999,7 @@
       </c>
       <c r="J177" s="24" t="n">
         <f aca="false">SUM(C177:I177)</f>
-        <v>153</v>
+        <v>225</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31089,19 +31089,19 @@
       <c r="B180" s="25"/>
       <c r="C180" s="24" t="n">
         <f aca="false">SUM(C176:C179)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D180" s="24" t="n">
         <f aca="false">SUM(D176:D179)</f>
-        <v>85.5</v>
+        <v>121.5</v>
       </c>
       <c r="E180" s="24" t="n">
         <f aca="false">SUM(E176:E179)</f>
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="F180" s="24" t="n">
         <f aca="false">SUM(F176:F179)</f>
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G180" s="24" t="n">
         <f aca="false">SUM(G176:G179)</f>
@@ -31117,7 +31117,7 @@
       </c>
       <c r="J180" s="24" t="n">
         <f aca="false">SUM(J176:J179)</f>
-        <v>349.5</v>
+        <v>429.5</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
